--- a/sample_data/products.xlsx
+++ b/sample_data/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,16 @@
           <t>店铺</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>主图</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>详情图</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,6 +485,16 @@
           <t>旗舰店</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>images/PROD001_main.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>images/PROD001_detail_1.jpg;images/PROD001_detail_2.jpg;images/PROD001_detail_3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +523,16 @@
           <t>专营店</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://cdn.example.com/images/PROD002.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://cdn.example.com/images/PROD002_detail_1.jpg;https://cdn.example.com/images/PROD002_detail_2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,7 +542,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>高仿奢侈品包包 原单复刻</t>
+          <t>高仿奢侈品包包 原单复刻爆款</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -531,6 +561,8 @@
           <t>旗舰店</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -555,6 +587,8 @@
           <t>专营店</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -567,6 +601,9 @@
           <t>纯棉T恤 夏季新款短袖</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>-10</v>
+      </c>
       <c r="D6" t="n">
         <v>-5</v>
       </c>
@@ -576,29 +613,44 @@
           <t>旗舰店</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PROD001</t>
+          <t>PROD006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>无线蓝牙耳机 重复SKU测试</t>
+          <t>运动鞋 轻便透气跑步鞋</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10000</v>
+        <v>299</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-100</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>数码配件</t>
+          <t>鞋靴</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>专营店</t>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>images/PROD001_main.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>images/PROD001_detail_1.jpg</t>
         </is>
       </c>
     </row>

--- a/sample_data/products.xlsx
+++ b/sample_data/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,6 +654,40 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PROD007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>纯棉衬衫 商务休闲长袖</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>159</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>服装</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>旗舰店</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://cdn.example.com/images/PROD007.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sample_data/products.xlsx
+++ b/sample_data/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,112 @@
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PROD008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>小尺寸图片测试商品</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>家居用品</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>images/PROD008_main.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>images/PROD008_detail_1.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PROD009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>损坏图片测试商品</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>199</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>数码配件</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>images/PROD009_main.jpg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PROD010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>大文件图片测试商品</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>299</v>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>箱包配饰</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>专营店</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>images/PROD010_main.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
